--- a/calculadoraWEB.xlsx
+++ b/calculadoraWEB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\googleDrive\docencia\GE\libro\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pruebasaluuclm-my.sharepoint.com/personal/diego_pedregal_uclm_es/Documents/cursoCorriente/docencia/GE/libroQuarto/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EEA557A-055F-4539-A96D-D26BAFBDD18A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{0CDCC24E-F33A-4DA6-B45A-9ABFA43EBE36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51649BD1-62DB-4C67-A1B2-1FDCF5827A7C}"/>
   <bookViews>
-    <workbookView xWindow="2235" yWindow="720" windowWidth="10335" windowHeight="7815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35250" yWindow="2550" windowWidth="7935" windowHeight="8265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Físicas" sheetId="1" r:id="rId1"/>
@@ -36,12 +36,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Tipos</t>
-  </si>
-  <si>
-    <t>Tabla IRPF 2018</t>
   </si>
   <si>
     <t>Sueldo bruto:</t>
@@ -68,9 +65,6 @@
     <t>Consumo:</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>IVA y especiales:</t>
   </si>
   <si>
@@ -84,6 +78,18 @@
   </si>
   <si>
     <t>Sobre sueldo bruto</t>
+  </si>
+  <si>
+    <t>Tabla IRPF 2024</t>
+  </si>
+  <si>
+    <t>Reducción general</t>
+  </si>
+  <si>
+    <t>Mínimo personal</t>
+  </si>
+  <si>
+    <t>Base imponible bruta</t>
   </si>
 </sst>
 </file>
@@ -106,29 +112,34 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Helvetica Neue"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -500,7 +511,8 @@
     <col min="7" max="8" width="11" customWidth="1"/>
     <col min="9" max="9" width="13.375" customWidth="1"/>
     <col min="10" max="10" width="12.625" customWidth="1"/>
-    <col min="11" max="25" width="10.5" customWidth="1"/>
+    <col min="11" max="11" width="12.125" customWidth="1"/>
+    <col min="12" max="25" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15.75" customHeight="1">
@@ -512,7 +524,7 @@
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
       <c r="F1" s="4" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
@@ -536,19 +548,17 @@
     </row>
     <row r="2" spans="1:25" ht="15.75" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="19">
-        <v>50000</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="B2" s="19"/>
       <c r="C2" s="7"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
       <c r="F2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="8" t="s">
         <v>3</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>4</v>
       </c>
       <c r="H2" s="8"/>
       <c r="I2" s="5"/>
@@ -571,11 +581,11 @@
     </row>
     <row r="3" spans="1:25" ht="15.75" customHeight="1">
       <c r="A3" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" s="10">
         <f>B2/(1-C4)</f>
-        <v>65445.02617801047</v>
+        <v>0</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="5"/>
@@ -590,15 +600,21 @@
         <v>0.19</v>
       </c>
       <c r="I3" s="5">
-        <f t="shared" ref="I3:I7" si="0">IF(G$9&gt;G3,G3-F3,MAX(G$9-F3,0))</f>
-        <v>12450</v>
+        <f t="shared" ref="I3:I8" si="0">IF(G$9&gt;G3,G3-F3,MAX(G$9-F3,0))</f>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <f t="shared" ref="J3:J7" si="1">I3*H3</f>
-        <v>2365.5</v>
-      </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
+        <f t="shared" ref="J3:J8" si="1">I3*H3</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <f t="shared" ref="K3:K8" si="2">IF(G$12&gt;G3,G3-F3,MAX(G$12-F3,0))</f>
+        <v>5500</v>
+      </c>
+      <c r="L3" s="5">
+        <f>K3*H3</f>
+        <v>1045</v>
+      </c>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
@@ -615,11 +631,11 @@
     </row>
     <row r="4" spans="1:25" ht="15.75" customHeight="1">
       <c r="A4" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" s="13">
         <f>B3-B2</f>
-        <v>15445.02617801047</v>
+        <v>0</v>
       </c>
       <c r="C4" s="20">
         <v>0.23599999999999999</v>
@@ -630,21 +646,27 @@
         <v>12450</v>
       </c>
       <c r="G4" s="11">
-        <v>20200</v>
+        <v>20199</v>
       </c>
       <c r="H4" s="12">
         <v>0.24</v>
       </c>
       <c r="I4" s="5">
         <f t="shared" si="0"/>
-        <v>7750</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
         <f t="shared" si="1"/>
-        <v>1860</v>
-      </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <f t="shared" ref="L4:L8" si="3">K4*H4</f>
+        <v>0</v>
+      </c>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
@@ -661,11 +683,11 @@
     </row>
     <row r="5" spans="1:25" ht="15.75" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" s="13">
         <f>C5*B3</f>
-        <v>3075.9162303664921</v>
+        <v>0</v>
       </c>
       <c r="C5" s="20">
         <v>4.7E-2</v>
@@ -676,21 +698,27 @@
         <v>20200</v>
       </c>
       <c r="G5" s="11">
-        <v>35200</v>
+        <v>35199</v>
       </c>
       <c r="H5" s="12">
         <v>0.3</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" si="0"/>
-        <v>14993.062827225134</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
         <f t="shared" si="1"/>
-        <v>4497.9188481675401</v>
-      </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
@@ -707,11 +735,11 @@
     </row>
     <row r="6" spans="1:25" ht="15.75" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" s="13">
         <f>J9</f>
-        <v>8723.418848167541</v>
+        <v>0</v>
       </c>
       <c r="C6" s="21"/>
       <c r="D6" s="4"/>
@@ -720,7 +748,7 @@
         <v>35200</v>
       </c>
       <c r="G6" s="11">
-        <v>60000</v>
+        <v>59999</v>
       </c>
       <c r="H6" s="12">
         <v>0.37</v>
@@ -733,8 +761,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
+      <c r="K6" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
@@ -751,22 +785,22 @@
     </row>
     <row r="7" spans="1:25" ht="15.75" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" s="13">
         <f>C7*(B2-B6)</f>
-        <v>33021.264921465969</v>
+        <v>0</v>
       </c>
       <c r="C7" s="20">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="11">
         <v>60000</v>
       </c>
-      <c r="G7" s="8" t="s">
-        <v>10</v>
+      <c r="G7" s="11">
+        <v>299999</v>
       </c>
       <c r="H7" s="12">
         <v>0.45</v>
@@ -779,8 +813,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
+      <c r="K7" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
@@ -797,24 +837,42 @@
     </row>
     <row r="8" spans="1:25" ht="15.75" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B8" s="13">
         <f>C8*B7</f>
-        <v>5943.8276858638737</v>
+        <v>0</v>
       </c>
       <c r="C8" s="20">
         <v>0.18</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
+      <c r="F8" s="11">
+        <v>300000</v>
+      </c>
+      <c r="G8" s="11">
+        <v>100000000</v>
+      </c>
+      <c r="H8" s="12">
+        <v>0.49</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
@@ -831,27 +889,30 @@
     </row>
     <row r="9" spans="1:25" ht="15.75" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B9" s="19"/>
       <c r="C9" s="7"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G9" s="5">
-        <f>(B2-B5)*0.75</f>
-        <v>35193.062827225134</v>
+        <f>G13-H13</f>
+        <v>-8498</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="5"/>
       <c r="J9" s="5">
-        <f>SUM(J3:J7)</f>
-        <v>8723.418848167541</v>
-      </c>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
+        <f>MAX(SUM(J3:J8)-L9, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5">
+        <f>SUM(L3:L8)</f>
+        <v>1045</v>
+      </c>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
@@ -868,15 +929,15 @@
     </row>
     <row r="10" spans="1:25" ht="21.75" customHeight="1">
       <c r="A10" s="14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" s="15">
         <f>B4+B5+B6+B8+B9</f>
-        <v>33188.188942408378</v>
-      </c>
-      <c r="C10" s="16">
+        <v>0</v>
+      </c>
+      <c r="C10" s="16" t="e">
         <f>B10/B3</f>
-        <v>0.50711552704000007</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -903,20 +964,24 @@
     </row>
     <row r="11" spans="1:25" ht="26.25" customHeight="1">
       <c r="A11" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B11" s="15">
         <f>B5+B6+B8+B9</f>
-        <v>17743.162764397908</v>
-      </c>
-      <c r="C11" s="16">
+        <v>0</v>
+      </c>
+      <c r="C11" s="16" t="e">
         <f>B11/B2</f>
-        <v>0.35486325528795815</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
+      <c r="F11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="4">
+        <v>2000</v>
+      </c>
       <c r="H11" s="4"/>
       <c r="I11" s="5"/>
       <c r="J11" s="4"/>
@@ -942,8 +1007,12 @@
       <c r="C12" s="18"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
+      <c r="F12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="4">
+        <v>5500</v>
+      </c>
       <c r="H12" s="4"/>
       <c r="I12" s="5"/>
       <c r="J12" s="4"/>
@@ -969,9 +1038,17 @@
       <c r="C13" s="18"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
+      <c r="F13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" s="5">
+        <f>B2-B5-G11</f>
+        <v>-2000</v>
+      </c>
+      <c r="H13" s="4">
+        <f>IF(G13+G11&lt;14047.5,6498,IF(G13+G11&lt;19747.5,6498-1.14*(G13-14047.5+G11),0))</f>
+        <v>6498</v>
+      </c>
       <c r="I13" s="5"/>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
@@ -1051,7 +1128,7 @@
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
+      <c r="G16" s="5"/>
       <c r="H16" s="4"/>
       <c r="I16" s="5"/>
       <c r="J16" s="4"/>
@@ -7360,7 +7437,6 @@
     <row r="999" customFormat="1" ht="15.75" customHeight="1"/>
     <row r="1000" customFormat="1" ht="15.75" customHeight="1"/>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/calculadoraWEB.xlsx
+++ b/calculadoraWEB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pruebasaluuclm-my.sharepoint.com/personal/diego_pedregal_uclm_es/Documents/cursoCorriente/docencia/GE/libroQuarto/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="113" documentId="13_ncr:1_{FAFC96D7-72FB-B841-B395-F5F9CD63B021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75B1886E-941F-49D5-B9AA-FDAB7967394B}"/>
+  <xr:revisionPtr revIDLastSave="119" documentId="13_ncr:1_{FAFC96D7-72FB-B841-B395-F5F9CD63B021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E826609-6CB6-CD4B-B48F-7713722E4A7E}"/>
   <bookViews>
-    <workbookView xWindow="45600" yWindow="2040" windowWidth="9435" windowHeight="9015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Físicas" sheetId="1" r:id="rId1"/>
@@ -101,7 +101,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -502,21 +502,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AB1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
     <col min="2" max="2" width="33.5" customWidth="1"/>
-    <col min="3" max="3" width="19.125" customWidth="1"/>
+    <col min="3" max="3" width="19.1640625" customWidth="1"/>
     <col min="4" max="5" width="11" customWidth="1"/>
     <col min="6" max="6" width="24.5" customWidth="1"/>
     <col min="7" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="13.375" customWidth="1"/>
-    <col min="10" max="10" width="12.625" customWidth="1"/>
-    <col min="11" max="11" width="12.125" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" customWidth="1"/>
+    <col min="10" max="10" width="12.6640625" customWidth="1"/>
+    <col min="11" max="11" width="12.1640625" customWidth="1"/>
     <col min="12" max="25" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="15.75" customHeight="1" thickBot="1">
+    <row r="1" spans="1:28" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -536,7 +536,7 @@
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
     </row>
-    <row r="2" spans="1:28" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
+    <row r="2" spans="1:28" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="9"/>
       <c r="C2" s="15"/>
       <c r="D2" s="10" t="s">
@@ -562,11 +562,13 @@
       <c r="AA2" s="1"/>
       <c r="AB2" s="1"/>
     </row>
-    <row r="3" spans="1:28" ht="15.75" customHeight="1" thickTop="1">
+    <row r="3" spans="1:28" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="16"/>
+      <c r="C3" s="16">
+        <v>20000</v>
+      </c>
       <c r="D3" s="11"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
@@ -586,11 +588,11 @@
       </c>
       <c r="X3" s="2">
         <f t="shared" ref="X3:X8" si="0">IF(V$9&gt;V3,V3-U3,MAX(V$9-U3,0))</f>
-        <v>0</v>
+        <v>12450</v>
       </c>
       <c r="Y3" s="2">
         <f t="shared" ref="Y3:Y8" si="1">X3*W3</f>
-        <v>0</v>
+        <v>2365.5</v>
       </c>
       <c r="Z3" s="2">
         <f t="shared" ref="Z3:Z8" si="2">IF(V$12&gt;V3,V3-U3,MAX(V$12-U3,0))</f>
@@ -602,13 +604,13 @@
       </c>
       <c r="AB3" s="1"/>
     </row>
-    <row r="4" spans="1:28" ht="15.75" customHeight="1">
+    <row r="4" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="17">
         <f>C3/(1-D5)</f>
-        <v>0</v>
+        <v>26178.010471204187</v>
       </c>
       <c r="D4" s="11"/>
       <c r="N4" s="1"/>
@@ -629,11 +631,11 @@
       </c>
       <c r="X4" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3204.8657068062821</v>
       </c>
       <c r="Y4" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>769.16776963350765</v>
       </c>
       <c r="Z4" s="2">
         <f t="shared" si="2"/>
@@ -645,13 +647,13 @@
       </c>
       <c r="AB4" s="1"/>
     </row>
-    <row r="5" spans="1:28" ht="15.75" customHeight="1">
+    <row r="5" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="18">
         <f>C4-C3</f>
-        <v>0</v>
+        <v>6178.0104712041866</v>
       </c>
       <c r="D5" s="12">
         <v>0.23599999999999999</v>
@@ -690,13 +692,13 @@
       </c>
       <c r="AB5" s="1"/>
     </row>
-    <row r="6" spans="1:28" ht="15.75" customHeight="1">
+    <row r="6" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="18">
         <f>D6*C4</f>
-        <v>0</v>
+        <v>1230.3664921465968</v>
       </c>
       <c r="D6" s="12">
         <v>4.7E-2</v>
@@ -735,13 +737,13 @@
       </c>
       <c r="AB6" s="1"/>
     </row>
-    <row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <row r="7" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="18">
         <f>Y9</f>
-        <v>0</v>
+        <v>2089.6677696335078</v>
       </c>
       <c r="D7" s="13"/>
       <c r="N7" s="1"/>
@@ -778,13 +780,13 @@
       </c>
       <c r="AB7" s="1"/>
     </row>
-    <row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <row r="8" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="18">
         <f>D8*(C3-C6-C7)</f>
-        <v>0</v>
+        <v>10007.979442931937</v>
       </c>
       <c r="D8" s="12">
         <v>0.6</v>
@@ -823,13 +825,13 @@
       </c>
       <c r="AB8" s="1"/>
     </row>
-    <row r="9" spans="1:28" ht="15.75" customHeight="1">
+    <row r="9" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="18">
         <f>D9*C8</f>
-        <v>0</v>
+        <v>1401.1171220104713</v>
       </c>
       <c r="D9" s="12">
         <v>0.14000000000000001</v>
@@ -846,13 +848,13 @@
       </c>
       <c r="V9" s="2">
         <f>V13-W13</f>
-        <v>-8498</v>
+        <v>15654.865706806282</v>
       </c>
       <c r="W9" s="1"/>
       <c r="X9" s="2"/>
       <c r="Y9" s="2">
         <f>MAX(SUM(Y3:Y8)-AA9, 0)</f>
-        <v>0</v>
+        <v>2089.6677696335078</v>
       </c>
       <c r="Z9" s="2"/>
       <c r="AA9" s="2">
@@ -861,7 +863,7 @@
       </c>
       <c r="AB9" s="1"/>
     </row>
-    <row r="10" spans="1:28" ht="21.75" customHeight="1" thickBot="1">
+    <row r="10" spans="1:28" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
         <v>15</v>
       </c>
@@ -883,17 +885,17 @@
       <c r="AA10" s="1"/>
       <c r="AB10" s="1"/>
     </row>
-    <row r="11" spans="1:28" ht="26.25" customHeight="1" thickTop="1" thickBot="1">
+    <row r="11" spans="1:28" ht="26.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="20" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="19">
         <f>C5+C6+C7+C9+C10</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="14" t="str">
+        <v>10899.161854994763</v>
+      </c>
+      <c r="D11" s="14">
         <f>IF(C3="","",C11/C4)</f>
-        <v/>
+        <v>0.41634798286079999</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -915,18 +917,18 @@
       <c r="AA11" s="1"/>
       <c r="AB11" s="1"/>
     </row>
-    <row r="12" spans="1:28" ht="24" customHeight="1" thickTop="1" thickBot="1">
+    <row r="12" spans="1:28" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
       <c r="B12" s="20" t="s">
         <v>17</v>
       </c>
       <c r="C12" s="19">
         <f>C6+C7+C9+C10</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="14" t="str">
+        <v>4721.1513837905759</v>
+      </c>
+      <c r="D12" s="14">
         <f>IF(C3="","",C12/C3)</f>
-        <v/>
+        <v>0.2360575691895288</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
@@ -948,7 +950,7 @@
       <c r="AA12" s="1"/>
       <c r="AB12" s="1"/>
     </row>
-    <row r="13" spans="1:28" ht="15.75" customHeight="1" thickTop="1">
+    <row r="13" spans="1:28" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="2"/>
       <c r="C13" s="6"/>
@@ -965,11 +967,11 @@
       </c>
       <c r="V13" s="2">
         <f>C3-C6-V11</f>
-        <v>-2000</v>
+        <v>16769.633507853403</v>
       </c>
       <c r="W13" s="1">
         <f>IF(V13+V11&lt;14047.5,6498,IF(V13+V11&lt;19747.5,6498-1.14*(V13-14047.5+V11),0))</f>
-        <v>6498</v>
+        <v>1114.7678010471209</v>
       </c>
       <c r="X13" s="2"/>
       <c r="Y13" s="1"/>
@@ -977,7 +979,7 @@
       <c r="AA13" s="1"/>
       <c r="AB13" s="1"/>
     </row>
-    <row r="14" spans="1:28" ht="15.75" customHeight="1">
+    <row r="14" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="2"/>
       <c r="C14" s="6"/>
@@ -998,7 +1000,7 @@
       <c r="AA14" s="1"/>
       <c r="AB14" s="1"/>
     </row>
-    <row r="15" spans="1:28" ht="15.75" customHeight="1">
+    <row r="15" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="2"/>
       <c r="C15" s="6"/>
@@ -1019,7 +1021,7 @@
       <c r="AA15" s="1"/>
       <c r="AB15" s="1"/>
     </row>
-    <row r="16" spans="1:28" ht="15.75" customHeight="1">
+    <row r="16" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="2"/>
       <c r="C16" s="6"/>
@@ -1040,7 +1042,7 @@
       <c r="AA16" s="1"/>
       <c r="AB16" s="1"/>
     </row>
-    <row r="17" spans="1:28" ht="15.75" customHeight="1">
+    <row r="17" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="2"/>
       <c r="C17" s="6"/>
@@ -1061,7 +1063,7 @@
       <c r="AA17" s="1"/>
       <c r="AB17" s="1"/>
     </row>
-    <row r="18" spans="1:28" ht="15.75" customHeight="1">
+    <row r="18" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="2"/>
       <c r="C18" s="6"/>
@@ -1082,7 +1084,7 @@
       <c r="AA18" s="1"/>
       <c r="AB18" s="1"/>
     </row>
-    <row r="19" spans="1:28" ht="15.75" customHeight="1">
+    <row r="19" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="2"/>
       <c r="C19" s="6"/>
@@ -1109,7 +1111,7 @@
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
     </row>
-    <row r="20" spans="1:28" ht="15.75" customHeight="1">
+    <row r="20" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="2"/>
       <c r="C20" s="6"/>
@@ -1136,7 +1138,7 @@
       <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
     </row>
-    <row r="21" spans="1:28" ht="15.75" customHeight="1">
+    <row r="21" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21" s="2"/>
       <c r="C21" s="6"/>
@@ -1163,7 +1165,7 @@
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
     </row>
-    <row r="22" spans="1:28" ht="15.75" customHeight="1">
+    <row r="22" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="2"/>
       <c r="C22" s="6"/>
@@ -1190,7 +1192,7 @@
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
     </row>
-    <row r="23" spans="1:28" ht="15.75" customHeight="1">
+    <row r="23" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="2"/>
       <c r="C23" s="6"/>
@@ -1217,7 +1219,7 @@
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
     </row>
-    <row r="24" spans="1:28" ht="15.75" customHeight="1">
+    <row r="24" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="2"/>
       <c r="C24" s="6"/>
@@ -1244,7 +1246,7 @@
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
     </row>
-    <row r="25" spans="1:28" ht="15.75" customHeight="1">
+    <row r="25" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="2"/>
       <c r="C25" s="6"/>
@@ -1271,7 +1273,7 @@
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
     </row>
-    <row r="26" spans="1:28" ht="15.75" customHeight="1">
+    <row r="26" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="B26" s="2"/>
       <c r="C26" s="6"/>
@@ -1298,7 +1300,7 @@
       <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
     </row>
-    <row r="27" spans="1:28" ht="15.75" customHeight="1">
+    <row r="27" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
       <c r="B27" s="2"/>
       <c r="C27" s="6"/>
@@ -1325,7 +1327,7 @@
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
     </row>
-    <row r="28" spans="1:28" ht="15.75" customHeight="1">
+    <row r="28" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="2"/>
       <c r="C28" s="6"/>
@@ -1352,7 +1354,7 @@
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
     </row>
-    <row r="29" spans="1:28" ht="15.75" customHeight="1">
+    <row r="29" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="2"/>
       <c r="C29" s="6"/>
@@ -1379,7 +1381,7 @@
       <c r="X29" s="1"/>
       <c r="Y29" s="1"/>
     </row>
-    <row r="30" spans="1:28" ht="15.75" customHeight="1">
+    <row r="30" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="B30" s="2"/>
       <c r="C30" s="6"/>
@@ -1406,7 +1408,7 @@
       <c r="X30" s="1"/>
       <c r="Y30" s="1"/>
     </row>
-    <row r="31" spans="1:28" ht="15.75" customHeight="1">
+    <row r="31" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="2"/>
       <c r="C31" s="6"/>
@@ -1433,7 +1435,7 @@
       <c r="X31" s="1"/>
       <c r="Y31" s="1"/>
     </row>
-    <row r="32" spans="1:28" ht="15.75" customHeight="1">
+    <row r="32" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="B32" s="2"/>
       <c r="C32" s="6"/>
@@ -1460,7 +1462,7 @@
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
     </row>
-    <row r="33" spans="1:25" ht="15.75" customHeight="1">
+    <row r="33" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
       <c r="B33" s="2"/>
       <c r="C33" s="6"/>
@@ -1487,7 +1489,7 @@
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
     </row>
-    <row r="34" spans="1:25" ht="15.75" customHeight="1">
+    <row r="34" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
       <c r="B34" s="2"/>
       <c r="C34" s="6"/>
@@ -1514,7 +1516,7 @@
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
     </row>
-    <row r="35" spans="1:25" ht="15.75" customHeight="1">
+    <row r="35" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
       <c r="B35" s="2"/>
       <c r="C35" s="6"/>
@@ -1541,7 +1543,7 @@
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
     </row>
-    <row r="36" spans="1:25" ht="15.75" customHeight="1">
+    <row r="36" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
       <c r="B36" s="2"/>
       <c r="C36" s="6"/>
@@ -1568,7 +1570,7 @@
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
     </row>
-    <row r="37" spans="1:25" ht="15.75" customHeight="1">
+    <row r="37" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
       <c r="B37" s="2"/>
       <c r="C37" s="6"/>
@@ -1595,7 +1597,7 @@
       <c r="X37" s="1"/>
       <c r="Y37" s="1"/>
     </row>
-    <row r="38" spans="1:25" ht="15.75" customHeight="1">
+    <row r="38" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1"/>
       <c r="B38" s="2"/>
       <c r="C38" s="6"/>
@@ -1622,7 +1624,7 @@
       <c r="X38" s="1"/>
       <c r="Y38" s="1"/>
     </row>
-    <row r="39" spans="1:25" ht="15.75" customHeight="1">
+    <row r="39" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1"/>
       <c r="B39" s="2"/>
       <c r="C39" s="6"/>
@@ -1649,7 +1651,7 @@
       <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
     </row>
-    <row r="40" spans="1:25" ht="15.75" customHeight="1">
+    <row r="40" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
       <c r="B40" s="2"/>
       <c r="C40" s="6"/>
@@ -1676,7 +1678,7 @@
       <c r="X40" s="1"/>
       <c r="Y40" s="1"/>
     </row>
-    <row r="41" spans="1:25" ht="15.75" customHeight="1">
+    <row r="41" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1"/>
       <c r="B41" s="2"/>
       <c r="C41" s="6"/>
@@ -1703,7 +1705,7 @@
       <c r="X41" s="1"/>
       <c r="Y41" s="1"/>
     </row>
-    <row r="42" spans="1:25" ht="15.75" customHeight="1">
+    <row r="42" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1"/>
       <c r="B42" s="2"/>
       <c r="C42" s="6"/>
@@ -1730,7 +1732,7 @@
       <c r="X42" s="1"/>
       <c r="Y42" s="1"/>
     </row>
-    <row r="43" spans="1:25" ht="15.75" customHeight="1">
+    <row r="43" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1"/>
       <c r="B43" s="2"/>
       <c r="C43" s="6"/>
@@ -1757,7 +1759,7 @@
       <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
     </row>
-    <row r="44" spans="1:25" ht="15.75" customHeight="1">
+    <row r="44" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1"/>
       <c r="B44" s="2"/>
       <c r="C44" s="6"/>
@@ -1784,7 +1786,7 @@
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
     </row>
-    <row r="45" spans="1:25" ht="15.75" customHeight="1">
+    <row r="45" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
       <c r="B45" s="2"/>
       <c r="C45" s="6"/>
@@ -1811,7 +1813,7 @@
       <c r="X45" s="1"/>
       <c r="Y45" s="1"/>
     </row>
-    <row r="46" spans="1:25" ht="15.75" customHeight="1">
+    <row r="46" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1"/>
       <c r="B46" s="2"/>
       <c r="C46" s="6"/>
@@ -1838,7 +1840,7 @@
       <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
     </row>
-    <row r="47" spans="1:25" ht="15.75" customHeight="1">
+    <row r="47" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1"/>
       <c r="B47" s="2"/>
       <c r="C47" s="6"/>
@@ -1865,7 +1867,7 @@
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
     </row>
-    <row r="48" spans="1:25" ht="15.75" customHeight="1">
+    <row r="48" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1"/>
       <c r="B48" s="2"/>
       <c r="C48" s="6"/>
@@ -1892,7 +1894,7 @@
       <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
     </row>
-    <row r="49" spans="1:25" ht="15.75" customHeight="1">
+    <row r="49" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1"/>
       <c r="B49" s="2"/>
       <c r="C49" s="6"/>
@@ -1919,7 +1921,7 @@
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
     </row>
-    <row r="50" spans="1:25" ht="15.75" customHeight="1">
+    <row r="50" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1"/>
       <c r="B50" s="2"/>
       <c r="C50" s="6"/>
@@ -1946,7 +1948,7 @@
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
     </row>
-    <row r="51" spans="1:25" ht="15.75" customHeight="1">
+    <row r="51" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1"/>
       <c r="B51" s="2"/>
       <c r="C51" s="6"/>
@@ -1973,7 +1975,7 @@
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
     </row>
-    <row r="52" spans="1:25" ht="15.75" customHeight="1">
+    <row r="52" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1"/>
       <c r="B52" s="2"/>
       <c r="C52" s="6"/>
@@ -2000,7 +2002,7 @@
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
     </row>
-    <row r="53" spans="1:25" ht="15.75" customHeight="1">
+    <row r="53" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1"/>
       <c r="B53" s="2"/>
       <c r="C53" s="6"/>
@@ -2027,7 +2029,7 @@
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
     </row>
-    <row r="54" spans="1:25" ht="15.75" customHeight="1">
+    <row r="54" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1"/>
       <c r="B54" s="2"/>
       <c r="C54" s="6"/>
@@ -2054,7 +2056,7 @@
       <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
     </row>
-    <row r="55" spans="1:25" ht="15.75" customHeight="1">
+    <row r="55" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
       <c r="B55" s="2"/>
       <c r="C55" s="6"/>
@@ -2081,7 +2083,7 @@
       <c r="X55" s="1"/>
       <c r="Y55" s="1"/>
     </row>
-    <row r="56" spans="1:25" ht="15.75" customHeight="1">
+    <row r="56" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1"/>
       <c r="B56" s="2"/>
       <c r="C56" s="6"/>
@@ -2108,7 +2110,7 @@
       <c r="X56" s="1"/>
       <c r="Y56" s="1"/>
     </row>
-    <row r="57" spans="1:25" ht="15.75" customHeight="1">
+    <row r="57" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
       <c r="B57" s="2"/>
       <c r="C57" s="6"/>
@@ -2135,7 +2137,7 @@
       <c r="X57" s="1"/>
       <c r="Y57" s="1"/>
     </row>
-    <row r="58" spans="1:25" ht="15.75" customHeight="1">
+    <row r="58" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1"/>
       <c r="B58" s="2"/>
       <c r="C58" s="6"/>
@@ -2162,7 +2164,7 @@
       <c r="X58" s="1"/>
       <c r="Y58" s="1"/>
     </row>
-    <row r="59" spans="1:25" ht="15.75" customHeight="1">
+    <row r="59" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
       <c r="B59" s="2"/>
       <c r="C59" s="6"/>
@@ -2189,7 +2191,7 @@
       <c r="X59" s="1"/>
       <c r="Y59" s="1"/>
     </row>
-    <row r="60" spans="1:25" ht="15.75" customHeight="1">
+    <row r="60" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1"/>
       <c r="B60" s="2"/>
       <c r="C60" s="6"/>
@@ -2216,7 +2218,7 @@
       <c r="X60" s="1"/>
       <c r="Y60" s="1"/>
     </row>
-    <row r="61" spans="1:25" ht="15.75" customHeight="1">
+    <row r="61" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
       <c r="B61" s="2"/>
       <c r="C61" s="6"/>
@@ -2243,7 +2245,7 @@
       <c r="X61" s="1"/>
       <c r="Y61" s="1"/>
     </row>
-    <row r="62" spans="1:25" ht="15.75" customHeight="1">
+    <row r="62" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1"/>
       <c r="B62" s="2"/>
       <c r="C62" s="6"/>
@@ -2270,7 +2272,7 @@
       <c r="X62" s="1"/>
       <c r="Y62" s="1"/>
     </row>
-    <row r="63" spans="1:25" ht="15.75" customHeight="1">
+    <row r="63" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1"/>
       <c r="B63" s="2"/>
       <c r="C63" s="6"/>
@@ -2297,7 +2299,7 @@
       <c r="X63" s="1"/>
       <c r="Y63" s="1"/>
     </row>
-    <row r="64" spans="1:25" ht="15.75" customHeight="1">
+    <row r="64" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="1"/>
       <c r="B64" s="2"/>
       <c r="C64" s="6"/>
@@ -2324,7 +2326,7 @@
       <c r="X64" s="1"/>
       <c r="Y64" s="1"/>
     </row>
-    <row r="65" spans="1:25" ht="15.75" customHeight="1">
+    <row r="65" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="1"/>
       <c r="B65" s="2"/>
       <c r="C65" s="6"/>
@@ -2351,7 +2353,7 @@
       <c r="X65" s="1"/>
       <c r="Y65" s="1"/>
     </row>
-    <row r="66" spans="1:25" ht="15.75" customHeight="1">
+    <row r="66" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1"/>
       <c r="B66" s="2"/>
       <c r="C66" s="6"/>
@@ -2378,7 +2380,7 @@
       <c r="X66" s="1"/>
       <c r="Y66" s="1"/>
     </row>
-    <row r="67" spans="1:25" ht="15.75" customHeight="1">
+    <row r="67" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="1"/>
       <c r="B67" s="2"/>
       <c r="C67" s="6"/>
@@ -2405,7 +2407,7 @@
       <c r="X67" s="1"/>
       <c r="Y67" s="1"/>
     </row>
-    <row r="68" spans="1:25" ht="15.75" customHeight="1">
+    <row r="68" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="1"/>
       <c r="B68" s="2"/>
       <c r="C68" s="6"/>
@@ -2432,7 +2434,7 @@
       <c r="X68" s="1"/>
       <c r="Y68" s="1"/>
     </row>
-    <row r="69" spans="1:25" ht="15.75" customHeight="1">
+    <row r="69" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="1"/>
       <c r="B69" s="2"/>
       <c r="C69" s="6"/>
@@ -2459,7 +2461,7 @@
       <c r="X69" s="1"/>
       <c r="Y69" s="1"/>
     </row>
-    <row r="70" spans="1:25" ht="15.75" customHeight="1">
+    <row r="70" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
       <c r="B70" s="2"/>
       <c r="C70" s="6"/>
@@ -2486,7 +2488,7 @@
       <c r="X70" s="1"/>
       <c r="Y70" s="1"/>
     </row>
-    <row r="71" spans="1:25" ht="15.75" customHeight="1">
+    <row r="71" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
       <c r="B71" s="2"/>
       <c r="C71" s="6"/>
@@ -2513,7 +2515,7 @@
       <c r="X71" s="1"/>
       <c r="Y71" s="1"/>
     </row>
-    <row r="72" spans="1:25" ht="15.75" customHeight="1">
+    <row r="72" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
       <c r="B72" s="2"/>
       <c r="C72" s="6"/>
@@ -2540,7 +2542,7 @@
       <c r="X72" s="1"/>
       <c r="Y72" s="1"/>
     </row>
-    <row r="73" spans="1:25" ht="15.75" customHeight="1">
+    <row r="73" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1"/>
       <c r="B73" s="2"/>
       <c r="C73" s="6"/>
@@ -2567,7 +2569,7 @@
       <c r="X73" s="1"/>
       <c r="Y73" s="1"/>
     </row>
-    <row r="74" spans="1:25" ht="15.75" customHeight="1">
+    <row r="74" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="1"/>
       <c r="B74" s="2"/>
       <c r="C74" s="6"/>
@@ -2594,7 +2596,7 @@
       <c r="X74" s="1"/>
       <c r="Y74" s="1"/>
     </row>
-    <row r="75" spans="1:25" ht="15.75" customHeight="1">
+    <row r="75" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
       <c r="B75" s="2"/>
       <c r="C75" s="6"/>
@@ -2621,7 +2623,7 @@
       <c r="X75" s="1"/>
       <c r="Y75" s="1"/>
     </row>
-    <row r="76" spans="1:25" ht="15.75" customHeight="1">
+    <row r="76" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
       <c r="B76" s="2"/>
       <c r="C76" s="6"/>
@@ -2648,7 +2650,7 @@
       <c r="X76" s="1"/>
       <c r="Y76" s="1"/>
     </row>
-    <row r="77" spans="1:25" ht="15.75" customHeight="1">
+    <row r="77" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
       <c r="B77" s="2"/>
       <c r="C77" s="6"/>
@@ -2675,7 +2677,7 @@
       <c r="X77" s="1"/>
       <c r="Y77" s="1"/>
     </row>
-    <row r="78" spans="1:25" ht="15.75" customHeight="1">
+    <row r="78" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="1"/>
       <c r="B78" s="2"/>
       <c r="C78" s="6"/>
@@ -2702,7 +2704,7 @@
       <c r="X78" s="1"/>
       <c r="Y78" s="1"/>
     </row>
-    <row r="79" spans="1:25" ht="15.75" customHeight="1">
+    <row r="79" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
       <c r="B79" s="2"/>
       <c r="C79" s="6"/>
@@ -2729,7 +2731,7 @@
       <c r="X79" s="1"/>
       <c r="Y79" s="1"/>
     </row>
-    <row r="80" spans="1:25" ht="15.75" customHeight="1">
+    <row r="80" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
       <c r="B80" s="2"/>
       <c r="C80" s="6"/>
@@ -2756,7 +2758,7 @@
       <c r="X80" s="1"/>
       <c r="Y80" s="1"/>
     </row>
-    <row r="81" spans="1:25" ht="15.75" customHeight="1">
+    <row r="81" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
       <c r="B81" s="2"/>
       <c r="C81" s="6"/>
@@ -2783,7 +2785,7 @@
       <c r="X81" s="1"/>
       <c r="Y81" s="1"/>
     </row>
-    <row r="82" spans="1:25" ht="15.75" customHeight="1">
+    <row r="82" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="1"/>
       <c r="B82" s="2"/>
       <c r="C82" s="6"/>
@@ -2810,7 +2812,7 @@
       <c r="X82" s="1"/>
       <c r="Y82" s="1"/>
     </row>
-    <row r="83" spans="1:25" ht="15.75" customHeight="1">
+    <row r="83" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="1"/>
       <c r="B83" s="2"/>
       <c r="C83" s="6"/>
@@ -2837,7 +2839,7 @@
       <c r="X83" s="1"/>
       <c r="Y83" s="1"/>
     </row>
-    <row r="84" spans="1:25" ht="15.75" customHeight="1">
+    <row r="84" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="1"/>
       <c r="B84" s="2"/>
       <c r="C84" s="6"/>
@@ -2864,7 +2866,7 @@
       <c r="X84" s="1"/>
       <c r="Y84" s="1"/>
     </row>
-    <row r="85" spans="1:25" ht="15.75" customHeight="1">
+    <row r="85" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="1"/>
       <c r="B85" s="2"/>
       <c r="C85" s="6"/>
@@ -2891,7 +2893,7 @@
       <c r="X85" s="1"/>
       <c r="Y85" s="1"/>
     </row>
-    <row r="86" spans="1:25" ht="15.75" customHeight="1">
+    <row r="86" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="1"/>
       <c r="B86" s="2"/>
       <c r="C86" s="6"/>
@@ -2918,7 +2920,7 @@
       <c r="X86" s="1"/>
       <c r="Y86" s="1"/>
     </row>
-    <row r="87" spans="1:25" ht="15.75" customHeight="1">
+    <row r="87" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
       <c r="B87" s="2"/>
       <c r="C87" s="6"/>
@@ -2945,7 +2947,7 @@
       <c r="X87" s="1"/>
       <c r="Y87" s="1"/>
     </row>
-    <row r="88" spans="1:25" ht="15.75" customHeight="1">
+    <row r="88" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
       <c r="B88" s="2"/>
       <c r="C88" s="6"/>
@@ -2972,7 +2974,7 @@
       <c r="X88" s="1"/>
       <c r="Y88" s="1"/>
     </row>
-    <row r="89" spans="1:25" ht="15.75" customHeight="1">
+    <row r="89" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
       <c r="B89" s="2"/>
       <c r="C89" s="6"/>
@@ -2999,7 +3001,7 @@
       <c r="X89" s="1"/>
       <c r="Y89" s="1"/>
     </row>
-    <row r="90" spans="1:25" ht="15.75" customHeight="1">
+    <row r="90" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="1"/>
       <c r="B90" s="2"/>
       <c r="C90" s="6"/>
@@ -3026,7 +3028,7 @@
       <c r="X90" s="1"/>
       <c r="Y90" s="1"/>
     </row>
-    <row r="91" spans="1:25" ht="15.75" customHeight="1">
+    <row r="91" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="1"/>
       <c r="B91" s="2"/>
       <c r="C91" s="6"/>
@@ -3053,7 +3055,7 @@
       <c r="X91" s="1"/>
       <c r="Y91" s="1"/>
     </row>
-    <row r="92" spans="1:25" ht="15.75" customHeight="1">
+    <row r="92" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="1"/>
       <c r="B92" s="2"/>
       <c r="C92" s="6"/>
@@ -3080,7 +3082,7 @@
       <c r="X92" s="1"/>
       <c r="Y92" s="1"/>
     </row>
-    <row r="93" spans="1:25" ht="15.75" customHeight="1">
+    <row r="93" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="1"/>
       <c r="B93" s="2"/>
       <c r="C93" s="6"/>
@@ -3107,7 +3109,7 @@
       <c r="X93" s="1"/>
       <c r="Y93" s="1"/>
     </row>
-    <row r="94" spans="1:25" ht="15.75" customHeight="1">
+    <row r="94" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="1"/>
       <c r="B94" s="2"/>
       <c r="C94" s="6"/>
@@ -3134,7 +3136,7 @@
       <c r="X94" s="1"/>
       <c r="Y94" s="1"/>
     </row>
-    <row r="95" spans="1:25" ht="15.75" customHeight="1">
+    <row r="95" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="1"/>
       <c r="B95" s="2"/>
       <c r="C95" s="6"/>
@@ -3161,7 +3163,7 @@
       <c r="X95" s="1"/>
       <c r="Y95" s="1"/>
     </row>
-    <row r="96" spans="1:25" ht="15.75" customHeight="1">
+    <row r="96" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="1"/>
       <c r="B96" s="2"/>
       <c r="C96" s="6"/>
@@ -3188,7 +3190,7 @@
       <c r="X96" s="1"/>
       <c r="Y96" s="1"/>
     </row>
-    <row r="97" spans="1:25" ht="15.75" customHeight="1">
+    <row r="97" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="1"/>
       <c r="B97" s="2"/>
       <c r="C97" s="6"/>
@@ -3215,7 +3217,7 @@
       <c r="X97" s="1"/>
       <c r="Y97" s="1"/>
     </row>
-    <row r="98" spans="1:25" ht="15.75" customHeight="1">
+    <row r="98" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="1"/>
       <c r="B98" s="2"/>
       <c r="C98" s="6"/>
@@ -3242,7 +3244,7 @@
       <c r="X98" s="1"/>
       <c r="Y98" s="1"/>
     </row>
-    <row r="99" spans="1:25" ht="15.75" customHeight="1">
+    <row r="99" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="1"/>
       <c r="B99" s="2"/>
       <c r="C99" s="6"/>
@@ -3269,7 +3271,7 @@
       <c r="X99" s="1"/>
       <c r="Y99" s="1"/>
     </row>
-    <row r="100" spans="1:25" ht="15.75" customHeight="1">
+    <row r="100" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
       <c r="B100" s="2"/>
       <c r="C100" s="6"/>
@@ -3296,7 +3298,7 @@
       <c r="X100" s="1"/>
       <c r="Y100" s="1"/>
     </row>
-    <row r="101" spans="1:25" ht="15.75" customHeight="1">
+    <row r="101" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
       <c r="B101" s="2"/>
       <c r="C101" s="6"/>
@@ -3323,7 +3325,7 @@
       <c r="X101" s="1"/>
       <c r="Y101" s="1"/>
     </row>
-    <row r="102" spans="1:25" ht="15.75" customHeight="1">
+    <row r="102" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
       <c r="B102" s="2"/>
       <c r="C102" s="6"/>
@@ -3350,7 +3352,7 @@
       <c r="X102" s="1"/>
       <c r="Y102" s="1"/>
     </row>
-    <row r="103" spans="1:25" ht="15.75" customHeight="1">
+    <row r="103" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="1"/>
       <c r="B103" s="2"/>
       <c r="C103" s="6"/>
@@ -3377,7 +3379,7 @@
       <c r="X103" s="1"/>
       <c r="Y103" s="1"/>
     </row>
-    <row r="104" spans="1:25" ht="15.75" customHeight="1">
+    <row r="104" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="1"/>
       <c r="B104" s="2"/>
       <c r="C104" s="6"/>
@@ -3404,7 +3406,7 @@
       <c r="X104" s="1"/>
       <c r="Y104" s="1"/>
     </row>
-    <row r="105" spans="1:25" ht="15.75" customHeight="1">
+    <row r="105" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="1"/>
       <c r="B105" s="2"/>
       <c r="C105" s="6"/>
@@ -3431,7 +3433,7 @@
       <c r="X105" s="1"/>
       <c r="Y105" s="1"/>
     </row>
-    <row r="106" spans="1:25" ht="15.75" customHeight="1">
+    <row r="106" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="1"/>
       <c r="B106" s="2"/>
       <c r="C106" s="6"/>
@@ -3458,7 +3460,7 @@
       <c r="X106" s="1"/>
       <c r="Y106" s="1"/>
     </row>
-    <row r="107" spans="1:25" ht="15.75" customHeight="1">
+    <row r="107" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="1"/>
       <c r="B107" s="2"/>
       <c r="C107" s="6"/>
@@ -3485,7 +3487,7 @@
       <c r="X107" s="1"/>
       <c r="Y107" s="1"/>
     </row>
-    <row r="108" spans="1:25" ht="15.75" customHeight="1">
+    <row r="108" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="1"/>
       <c r="B108" s="2"/>
       <c r="C108" s="6"/>
@@ -3512,7 +3514,7 @@
       <c r="X108" s="1"/>
       <c r="Y108" s="1"/>
     </row>
-    <row r="109" spans="1:25" ht="15.75" customHeight="1">
+    <row r="109" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="1"/>
       <c r="B109" s="2"/>
       <c r="C109" s="6"/>
@@ -3539,7 +3541,7 @@
       <c r="X109" s="1"/>
       <c r="Y109" s="1"/>
     </row>
-    <row r="110" spans="1:25" ht="15.75" customHeight="1">
+    <row r="110" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="1"/>
       <c r="B110" s="2"/>
       <c r="C110" s="6"/>
@@ -3566,7 +3568,7 @@
       <c r="X110" s="1"/>
       <c r="Y110" s="1"/>
     </row>
-    <row r="111" spans="1:25" ht="15.75" customHeight="1">
+    <row r="111" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="1"/>
       <c r="B111" s="2"/>
       <c r="C111" s="6"/>
@@ -3593,7 +3595,7 @@
       <c r="X111" s="1"/>
       <c r="Y111" s="1"/>
     </row>
-    <row r="112" spans="1:25" ht="15.75" customHeight="1">
+    <row r="112" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="1"/>
       <c r="B112" s="2"/>
       <c r="C112" s="6"/>
@@ -3620,7 +3622,7 @@
       <c r="X112" s="1"/>
       <c r="Y112" s="1"/>
     </row>
-    <row r="113" spans="1:25" ht="15.75" customHeight="1">
+    <row r="113" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="1"/>
       <c r="B113" s="2"/>
       <c r="C113" s="6"/>
@@ -3647,7 +3649,7 @@
       <c r="X113" s="1"/>
       <c r="Y113" s="1"/>
     </row>
-    <row r="114" spans="1:25" ht="15.75" customHeight="1">
+    <row r="114" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="1"/>
       <c r="B114" s="2"/>
       <c r="C114" s="6"/>
@@ -3674,7 +3676,7 @@
       <c r="X114" s="1"/>
       <c r="Y114" s="1"/>
     </row>
-    <row r="115" spans="1:25" ht="15.75" customHeight="1">
+    <row r="115" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="1"/>
       <c r="B115" s="2"/>
       <c r="C115" s="6"/>
@@ -3701,7 +3703,7 @@
       <c r="X115" s="1"/>
       <c r="Y115" s="1"/>
     </row>
-    <row r="116" spans="1:25" ht="15.75" customHeight="1">
+    <row r="116" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="1"/>
       <c r="B116" s="2"/>
       <c r="C116" s="6"/>
@@ -3728,7 +3730,7 @@
       <c r="X116" s="1"/>
       <c r="Y116" s="1"/>
     </row>
-    <row r="117" spans="1:25" ht="15.75" customHeight="1">
+    <row r="117" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="1"/>
       <c r="B117" s="2"/>
       <c r="C117" s="6"/>
@@ -3755,7 +3757,7 @@
       <c r="X117" s="1"/>
       <c r="Y117" s="1"/>
     </row>
-    <row r="118" spans="1:25" ht="15.75" customHeight="1">
+    <row r="118" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="1"/>
       <c r="B118" s="2"/>
       <c r="C118" s="6"/>
@@ -3782,7 +3784,7 @@
       <c r="X118" s="1"/>
       <c r="Y118" s="1"/>
     </row>
-    <row r="119" spans="1:25" ht="15.75" customHeight="1">
+    <row r="119" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="1"/>
       <c r="B119" s="2"/>
       <c r="C119" s="6"/>
@@ -3809,7 +3811,7 @@
       <c r="X119" s="1"/>
       <c r="Y119" s="1"/>
     </row>
-    <row r="120" spans="1:25" ht="15.75" customHeight="1">
+    <row r="120" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="1"/>
       <c r="B120" s="2"/>
       <c r="C120" s="6"/>
@@ -3836,7 +3838,7 @@
       <c r="X120" s="1"/>
       <c r="Y120" s="1"/>
     </row>
-    <row r="121" spans="1:25" ht="15.75" customHeight="1">
+    <row r="121" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="1"/>
       <c r="B121" s="2"/>
       <c r="C121" s="6"/>
@@ -3863,7 +3865,7 @@
       <c r="X121" s="1"/>
       <c r="Y121" s="1"/>
     </row>
-    <row r="122" spans="1:25" ht="15.75" customHeight="1">
+    <row r="122" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="1"/>
       <c r="B122" s="2"/>
       <c r="C122" s="6"/>
@@ -3890,7 +3892,7 @@
       <c r="X122" s="1"/>
       <c r="Y122" s="1"/>
     </row>
-    <row r="123" spans="1:25" ht="15.75" customHeight="1">
+    <row r="123" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="1"/>
       <c r="B123" s="2"/>
       <c r="C123" s="6"/>
@@ -3917,7 +3919,7 @@
       <c r="X123" s="1"/>
       <c r="Y123" s="1"/>
     </row>
-    <row r="124" spans="1:25" ht="15.75" customHeight="1">
+    <row r="124" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="1"/>
       <c r="B124" s="2"/>
       <c r="C124" s="6"/>
@@ -3944,7 +3946,7 @@
       <c r="X124" s="1"/>
       <c r="Y124" s="1"/>
     </row>
-    <row r="125" spans="1:25" ht="15.75" customHeight="1">
+    <row r="125" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="1"/>
       <c r="B125" s="2"/>
       <c r="C125" s="6"/>
@@ -3971,7 +3973,7 @@
       <c r="X125" s="1"/>
       <c r="Y125" s="1"/>
     </row>
-    <row r="126" spans="1:25" ht="15.75" customHeight="1">
+    <row r="126" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="1"/>
       <c r="B126" s="2"/>
       <c r="C126" s="6"/>
@@ -3998,7 +4000,7 @@
       <c r="X126" s="1"/>
       <c r="Y126" s="1"/>
     </row>
-    <row r="127" spans="1:25" ht="15.75" customHeight="1">
+    <row r="127" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="1"/>
       <c r="B127" s="2"/>
       <c r="C127" s="6"/>
@@ -4025,7 +4027,7 @@
       <c r="X127" s="1"/>
       <c r="Y127" s="1"/>
     </row>
-    <row r="128" spans="1:25" ht="15.75" customHeight="1">
+    <row r="128" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="1"/>
       <c r="B128" s="2"/>
       <c r="C128" s="6"/>
@@ -4052,7 +4054,7 @@
       <c r="X128" s="1"/>
       <c r="Y128" s="1"/>
     </row>
-    <row r="129" spans="1:25" ht="15.75" customHeight="1">
+    <row r="129" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="1"/>
       <c r="B129" s="2"/>
       <c r="C129" s="6"/>
@@ -4079,7 +4081,7 @@
       <c r="X129" s="1"/>
       <c r="Y129" s="1"/>
     </row>
-    <row r="130" spans="1:25" ht="15.75" customHeight="1">
+    <row r="130" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="1"/>
       <c r="B130" s="2"/>
       <c r="C130" s="6"/>
@@ -4106,7 +4108,7 @@
       <c r="X130" s="1"/>
       <c r="Y130" s="1"/>
     </row>
-    <row r="131" spans="1:25" ht="15.75" customHeight="1">
+    <row r="131" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="1"/>
       <c r="B131" s="2"/>
       <c r="C131" s="6"/>
@@ -4133,7 +4135,7 @@
       <c r="X131" s="1"/>
       <c r="Y131" s="1"/>
     </row>
-    <row r="132" spans="1:25" ht="15.75" customHeight="1">
+    <row r="132" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="1"/>
       <c r="B132" s="2"/>
       <c r="C132" s="6"/>
@@ -4160,7 +4162,7 @@
       <c r="X132" s="1"/>
       <c r="Y132" s="1"/>
     </row>
-    <row r="133" spans="1:25" ht="15.75" customHeight="1">
+    <row r="133" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="1"/>
       <c r="B133" s="2"/>
       <c r="C133" s="6"/>
@@ -4187,7 +4189,7 @@
       <c r="X133" s="1"/>
       <c r="Y133" s="1"/>
     </row>
-    <row r="134" spans="1:25" ht="15.75" customHeight="1">
+    <row r="134" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="1"/>
       <c r="B134" s="2"/>
       <c r="C134" s="6"/>
@@ -4214,7 +4216,7 @@
       <c r="X134" s="1"/>
       <c r="Y134" s="1"/>
     </row>
-    <row r="135" spans="1:25" ht="15.75" customHeight="1">
+    <row r="135" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="1"/>
       <c r="B135" s="2"/>
       <c r="C135" s="6"/>
@@ -4241,7 +4243,7 @@
       <c r="X135" s="1"/>
       <c r="Y135" s="1"/>
     </row>
-    <row r="136" spans="1:25" ht="15.75" customHeight="1">
+    <row r="136" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="1"/>
       <c r="B136" s="2"/>
       <c r="C136" s="6"/>
@@ -4268,7 +4270,7 @@
       <c r="X136" s="1"/>
       <c r="Y136" s="1"/>
     </row>
-    <row r="137" spans="1:25" ht="15.75" customHeight="1">
+    <row r="137" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="1"/>
       <c r="B137" s="2"/>
       <c r="C137" s="6"/>
@@ -4295,7 +4297,7 @@
       <c r="X137" s="1"/>
       <c r="Y137" s="1"/>
     </row>
-    <row r="138" spans="1:25" ht="15.75" customHeight="1">
+    <row r="138" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="1"/>
       <c r="B138" s="2"/>
       <c r="C138" s="6"/>
@@ -4322,7 +4324,7 @@
       <c r="X138" s="1"/>
       <c r="Y138" s="1"/>
     </row>
-    <row r="139" spans="1:25" ht="15.75" customHeight="1">
+    <row r="139" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="1"/>
       <c r="B139" s="2"/>
       <c r="C139" s="6"/>
@@ -4349,7 +4351,7 @@
       <c r="X139" s="1"/>
       <c r="Y139" s="1"/>
     </row>
-    <row r="140" spans="1:25" ht="15.75" customHeight="1">
+    <row r="140" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="1"/>
       <c r="B140" s="2"/>
       <c r="C140" s="6"/>
@@ -4376,7 +4378,7 @@
       <c r="X140" s="1"/>
       <c r="Y140" s="1"/>
     </row>
-    <row r="141" spans="1:25" ht="15.75" customHeight="1">
+    <row r="141" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="1"/>
       <c r="B141" s="2"/>
       <c r="C141" s="6"/>
@@ -4403,7 +4405,7 @@
       <c r="X141" s="1"/>
       <c r="Y141" s="1"/>
     </row>
-    <row r="142" spans="1:25" ht="15.75" customHeight="1">
+    <row r="142" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="1"/>
       <c r="B142" s="2"/>
       <c r="C142" s="6"/>
@@ -4430,7 +4432,7 @@
       <c r="X142" s="1"/>
       <c r="Y142" s="1"/>
     </row>
-    <row r="143" spans="1:25" ht="15.75" customHeight="1">
+    <row r="143" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="1"/>
       <c r="B143" s="2"/>
       <c r="C143" s="6"/>
@@ -4457,7 +4459,7 @@
       <c r="X143" s="1"/>
       <c r="Y143" s="1"/>
     </row>
-    <row r="144" spans="1:25" ht="15.75" customHeight="1">
+    <row r="144" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="1"/>
       <c r="B144" s="2"/>
       <c r="C144" s="6"/>
@@ -4484,7 +4486,7 @@
       <c r="X144" s="1"/>
       <c r="Y144" s="1"/>
     </row>
-    <row r="145" spans="1:25" ht="15.75" customHeight="1">
+    <row r="145" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="1"/>
       <c r="B145" s="2"/>
       <c r="C145" s="6"/>
@@ -4511,7 +4513,7 @@
       <c r="X145" s="1"/>
       <c r="Y145" s="1"/>
     </row>
-    <row r="146" spans="1:25" ht="15.75" customHeight="1">
+    <row r="146" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="1"/>
       <c r="B146" s="2"/>
       <c r="C146" s="6"/>
@@ -4538,7 +4540,7 @@
       <c r="X146" s="1"/>
       <c r="Y146" s="1"/>
     </row>
-    <row r="147" spans="1:25" ht="15.75" customHeight="1">
+    <row r="147" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="1"/>
       <c r="B147" s="2"/>
       <c r="C147" s="6"/>
@@ -4565,7 +4567,7 @@
       <c r="X147" s="1"/>
       <c r="Y147" s="1"/>
     </row>
-    <row r="148" spans="1:25" ht="15.75" customHeight="1">
+    <row r="148" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="1"/>
       <c r="B148" s="2"/>
       <c r="C148" s="6"/>
@@ -4592,7 +4594,7 @@
       <c r="X148" s="1"/>
       <c r="Y148" s="1"/>
     </row>
-    <row r="149" spans="1:25" ht="15.75" customHeight="1">
+    <row r="149" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="1"/>
       <c r="B149" s="2"/>
       <c r="C149" s="6"/>
@@ -4619,7 +4621,7 @@
       <c r="X149" s="1"/>
       <c r="Y149" s="1"/>
     </row>
-    <row r="150" spans="1:25" ht="15.75" customHeight="1">
+    <row r="150" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="1"/>
       <c r="B150" s="2"/>
       <c r="C150" s="6"/>
@@ -4646,7 +4648,7 @@
       <c r="X150" s="1"/>
       <c r="Y150" s="1"/>
     </row>
-    <row r="151" spans="1:25" ht="15.75" customHeight="1">
+    <row r="151" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="1"/>
       <c r="B151" s="2"/>
       <c r="C151" s="6"/>
@@ -4673,7 +4675,7 @@
       <c r="X151" s="1"/>
       <c r="Y151" s="1"/>
     </row>
-    <row r="152" spans="1:25" ht="15.75" customHeight="1">
+    <row r="152" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="1"/>
       <c r="B152" s="2"/>
       <c r="C152" s="6"/>
@@ -4700,7 +4702,7 @@
       <c r="X152" s="1"/>
       <c r="Y152" s="1"/>
     </row>
-    <row r="153" spans="1:25" ht="15.75" customHeight="1">
+    <row r="153" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="1"/>
       <c r="B153" s="2"/>
       <c r="C153" s="6"/>
@@ -4727,7 +4729,7 @@
       <c r="X153" s="1"/>
       <c r="Y153" s="1"/>
     </row>
-    <row r="154" spans="1:25" ht="15.75" customHeight="1">
+    <row r="154" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="1"/>
       <c r="B154" s="2"/>
       <c r="C154" s="6"/>
@@ -4754,7 +4756,7 @@
       <c r="X154" s="1"/>
       <c r="Y154" s="1"/>
     </row>
-    <row r="155" spans="1:25" ht="15.75" customHeight="1">
+    <row r="155" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="1"/>
       <c r="B155" s="2"/>
       <c r="C155" s="6"/>
@@ -4781,7 +4783,7 @@
       <c r="X155" s="1"/>
       <c r="Y155" s="1"/>
     </row>
-    <row r="156" spans="1:25" ht="15.75" customHeight="1">
+    <row r="156" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="1"/>
       <c r="B156" s="2"/>
       <c r="C156" s="6"/>
@@ -4808,7 +4810,7 @@
       <c r="X156" s="1"/>
       <c r="Y156" s="1"/>
     </row>
-    <row r="157" spans="1:25" ht="15.75" customHeight="1">
+    <row r="157" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="1"/>
       <c r="B157" s="2"/>
       <c r="C157" s="6"/>
@@ -4835,7 +4837,7 @@
       <c r="X157" s="1"/>
       <c r="Y157" s="1"/>
     </row>
-    <row r="158" spans="1:25" ht="15.75" customHeight="1">
+    <row r="158" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="1"/>
       <c r="B158" s="2"/>
       <c r="C158" s="6"/>
@@ -4862,7 +4864,7 @@
       <c r="X158" s="1"/>
       <c r="Y158" s="1"/>
     </row>
-    <row r="159" spans="1:25" ht="15.75" customHeight="1">
+    <row r="159" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="1"/>
       <c r="B159" s="2"/>
       <c r="C159" s="6"/>
@@ -4889,7 +4891,7 @@
       <c r="X159" s="1"/>
       <c r="Y159" s="1"/>
     </row>
-    <row r="160" spans="1:25" ht="15.75" customHeight="1">
+    <row r="160" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="1"/>
       <c r="B160" s="2"/>
       <c r="C160" s="6"/>
@@ -4916,7 +4918,7 @@
       <c r="X160" s="1"/>
       <c r="Y160" s="1"/>
     </row>
-    <row r="161" spans="1:25" ht="15.75" customHeight="1">
+    <row r="161" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="1"/>
       <c r="B161" s="2"/>
       <c r="C161" s="6"/>
@@ -4943,7 +4945,7 @@
       <c r="X161" s="1"/>
       <c r="Y161" s="1"/>
     </row>
-    <row r="162" spans="1:25" ht="15.75" customHeight="1">
+    <row r="162" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="1"/>
       <c r="B162" s="2"/>
       <c r="C162" s="6"/>
@@ -4970,7 +4972,7 @@
       <c r="X162" s="1"/>
       <c r="Y162" s="1"/>
     </row>
-    <row r="163" spans="1:25" ht="15.75" customHeight="1">
+    <row r="163" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="1"/>
       <c r="B163" s="2"/>
       <c r="C163" s="6"/>
@@ -4997,7 +4999,7 @@
       <c r="X163" s="1"/>
       <c r="Y163" s="1"/>
     </row>
-    <row r="164" spans="1:25" ht="15.75" customHeight="1">
+    <row r="164" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="1"/>
       <c r="B164" s="2"/>
       <c r="C164" s="6"/>
@@ -5024,7 +5026,7 @@
       <c r="X164" s="1"/>
       <c r="Y164" s="1"/>
     </row>
-    <row r="165" spans="1:25" ht="15.75" customHeight="1">
+    <row r="165" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="1"/>
       <c r="B165" s="2"/>
       <c r="C165" s="6"/>
@@ -5051,7 +5053,7 @@
       <c r="X165" s="1"/>
       <c r="Y165" s="1"/>
     </row>
-    <row r="166" spans="1:25" ht="15.75" customHeight="1">
+    <row r="166" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="1"/>
       <c r="B166" s="2"/>
       <c r="C166" s="6"/>
@@ -5078,7 +5080,7 @@
       <c r="X166" s="1"/>
       <c r="Y166" s="1"/>
     </row>
-    <row r="167" spans="1:25" ht="15.75" customHeight="1">
+    <row r="167" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="1"/>
       <c r="B167" s="2"/>
       <c r="C167" s="6"/>
@@ -5105,7 +5107,7 @@
       <c r="X167" s="1"/>
       <c r="Y167" s="1"/>
     </row>
-    <row r="168" spans="1:25" ht="15.75" customHeight="1">
+    <row r="168" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="1"/>
       <c r="B168" s="2"/>
       <c r="C168" s="6"/>
@@ -5132,7 +5134,7 @@
       <c r="X168" s="1"/>
       <c r="Y168" s="1"/>
     </row>
-    <row r="169" spans="1:25" ht="15.75" customHeight="1">
+    <row r="169" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="1"/>
       <c r="B169" s="2"/>
       <c r="C169" s="6"/>
@@ -5159,7 +5161,7 @@
       <c r="X169" s="1"/>
       <c r="Y169" s="1"/>
     </row>
-    <row r="170" spans="1:25" ht="15.75" customHeight="1">
+    <row r="170" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="1"/>
       <c r="B170" s="2"/>
       <c r="C170" s="6"/>
@@ -5186,7 +5188,7 @@
       <c r="X170" s="1"/>
       <c r="Y170" s="1"/>
     </row>
-    <row r="171" spans="1:25" ht="15.75" customHeight="1">
+    <row r="171" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="1"/>
       <c r="B171" s="2"/>
       <c r="C171" s="6"/>
@@ -5213,7 +5215,7 @@
       <c r="X171" s="1"/>
       <c r="Y171" s="1"/>
     </row>
-    <row r="172" spans="1:25" ht="15.75" customHeight="1">
+    <row r="172" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="1"/>
       <c r="B172" s="2"/>
       <c r="C172" s="6"/>
@@ -5240,7 +5242,7 @@
       <c r="X172" s="1"/>
       <c r="Y172" s="1"/>
     </row>
-    <row r="173" spans="1:25" ht="15.75" customHeight="1">
+    <row r="173" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="1"/>
       <c r="B173" s="2"/>
       <c r="C173" s="6"/>
@@ -5267,7 +5269,7 @@
       <c r="X173" s="1"/>
       <c r="Y173" s="1"/>
     </row>
-    <row r="174" spans="1:25" ht="15.75" customHeight="1">
+    <row r="174" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="1"/>
       <c r="B174" s="2"/>
       <c r="C174" s="6"/>
@@ -5294,7 +5296,7 @@
       <c r="X174" s="1"/>
       <c r="Y174" s="1"/>
     </row>
-    <row r="175" spans="1:25" ht="15.75" customHeight="1">
+    <row r="175" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="1"/>
       <c r="B175" s="2"/>
       <c r="C175" s="6"/>
@@ -5321,7 +5323,7 @@
       <c r="X175" s="1"/>
       <c r="Y175" s="1"/>
     </row>
-    <row r="176" spans="1:25" ht="15.75" customHeight="1">
+    <row r="176" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="1"/>
       <c r="B176" s="2"/>
       <c r="C176" s="6"/>
@@ -5348,7 +5350,7 @@
       <c r="X176" s="1"/>
       <c r="Y176" s="1"/>
     </row>
-    <row r="177" spans="1:25" ht="15.75" customHeight="1">
+    <row r="177" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="1"/>
       <c r="B177" s="2"/>
       <c r="C177" s="6"/>
@@ -5375,7 +5377,7 @@
       <c r="X177" s="1"/>
       <c r="Y177" s="1"/>
     </row>
-    <row r="178" spans="1:25" ht="15.75" customHeight="1">
+    <row r="178" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="1"/>
       <c r="B178" s="2"/>
       <c r="C178" s="6"/>
@@ -5402,7 +5404,7 @@
       <c r="X178" s="1"/>
       <c r="Y178" s="1"/>
     </row>
-    <row r="179" spans="1:25" ht="15.75" customHeight="1">
+    <row r="179" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="1"/>
       <c r="B179" s="2"/>
       <c r="C179" s="6"/>
@@ -5429,7 +5431,7 @@
       <c r="X179" s="1"/>
       <c r="Y179" s="1"/>
     </row>
-    <row r="180" spans="1:25" ht="15.75" customHeight="1">
+    <row r="180" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="1"/>
       <c r="B180" s="2"/>
       <c r="C180" s="6"/>
@@ -5456,7 +5458,7 @@
       <c r="X180" s="1"/>
       <c r="Y180" s="1"/>
     </row>
-    <row r="181" spans="1:25" ht="15.75" customHeight="1">
+    <row r="181" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="1"/>
       <c r="B181" s="2"/>
       <c r="C181" s="6"/>
@@ -5483,7 +5485,7 @@
       <c r="X181" s="1"/>
       <c r="Y181" s="1"/>
     </row>
-    <row r="182" spans="1:25" ht="15.75" customHeight="1">
+    <row r="182" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="1"/>
       <c r="B182" s="2"/>
       <c r="C182" s="6"/>
@@ -5510,7 +5512,7 @@
       <c r="X182" s="1"/>
       <c r="Y182" s="1"/>
     </row>
-    <row r="183" spans="1:25" ht="15.75" customHeight="1">
+    <row r="183" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="1"/>
       <c r="B183" s="2"/>
       <c r="C183" s="6"/>
@@ -5537,7 +5539,7 @@
       <c r="X183" s="1"/>
       <c r="Y183" s="1"/>
     </row>
-    <row r="184" spans="1:25" ht="15.75" customHeight="1">
+    <row r="184" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="1"/>
       <c r="B184" s="2"/>
       <c r="C184" s="6"/>
@@ -5564,7 +5566,7 @@
       <c r="X184" s="1"/>
       <c r="Y184" s="1"/>
     </row>
-    <row r="185" spans="1:25" ht="15.75" customHeight="1">
+    <row r="185" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="1"/>
       <c r="B185" s="2"/>
       <c r="C185" s="6"/>
@@ -5591,7 +5593,7 @@
       <c r="X185" s="1"/>
       <c r="Y185" s="1"/>
     </row>
-    <row r="186" spans="1:25" ht="15.75" customHeight="1">
+    <row r="186" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="1"/>
       <c r="B186" s="2"/>
       <c r="C186" s="6"/>
@@ -5618,7 +5620,7 @@
       <c r="X186" s="1"/>
       <c r="Y186" s="1"/>
     </row>
-    <row r="187" spans="1:25" ht="15.75" customHeight="1">
+    <row r="187" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="1"/>
       <c r="B187" s="2"/>
       <c r="C187" s="6"/>
@@ -5645,7 +5647,7 @@
       <c r="X187" s="1"/>
       <c r="Y187" s="1"/>
     </row>
-    <row r="188" spans="1:25" ht="15.75" customHeight="1">
+    <row r="188" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="1"/>
       <c r="B188" s="2"/>
       <c r="C188" s="6"/>
@@ -5672,7 +5674,7 @@
       <c r="X188" s="1"/>
       <c r="Y188" s="1"/>
     </row>
-    <row r="189" spans="1:25" ht="15.75" customHeight="1">
+    <row r="189" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="1"/>
       <c r="B189" s="2"/>
       <c r="C189" s="6"/>
@@ -5699,7 +5701,7 @@
       <c r="X189" s="1"/>
       <c r="Y189" s="1"/>
     </row>
-    <row r="190" spans="1:25" ht="15.75" customHeight="1">
+    <row r="190" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="1"/>
       <c r="B190" s="2"/>
       <c r="C190" s="6"/>
@@ -5726,7 +5728,7 @@
       <c r="X190" s="1"/>
       <c r="Y190" s="1"/>
     </row>
-    <row r="191" spans="1:25" ht="15.75" customHeight="1">
+    <row r="191" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="1"/>
       <c r="B191" s="2"/>
       <c r="C191" s="6"/>
@@ -5753,7 +5755,7 @@
       <c r="X191" s="1"/>
       <c r="Y191" s="1"/>
     </row>
-    <row r="192" spans="1:25" ht="15.75" customHeight="1">
+    <row r="192" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="1"/>
       <c r="B192" s="2"/>
       <c r="C192" s="6"/>
@@ -5780,7 +5782,7 @@
       <c r="X192" s="1"/>
       <c r="Y192" s="1"/>
     </row>
-    <row r="193" spans="1:25" ht="15.75" customHeight="1">
+    <row r="193" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="1"/>
       <c r="B193" s="2"/>
       <c r="C193" s="6"/>
@@ -5807,7 +5809,7 @@
       <c r="X193" s="1"/>
       <c r="Y193" s="1"/>
     </row>
-    <row r="194" spans="1:25" ht="15.75" customHeight="1">
+    <row r="194" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="1"/>
       <c r="B194" s="2"/>
       <c r="C194" s="6"/>
@@ -5834,7 +5836,7 @@
       <c r="X194" s="1"/>
       <c r="Y194" s="1"/>
     </row>
-    <row r="195" spans="1:25" ht="15.75" customHeight="1">
+    <row r="195" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="1"/>
       <c r="B195" s="2"/>
       <c r="C195" s="6"/>
@@ -5861,7 +5863,7 @@
       <c r="X195" s="1"/>
       <c r="Y195" s="1"/>
     </row>
-    <row r="196" spans="1:25" ht="15.75" customHeight="1">
+    <row r="196" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="1"/>
       <c r="B196" s="2"/>
       <c r="C196" s="6"/>
@@ -5888,7 +5890,7 @@
       <c r="X196" s="1"/>
       <c r="Y196" s="1"/>
     </row>
-    <row r="197" spans="1:25" ht="15.75" customHeight="1">
+    <row r="197" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="1"/>
       <c r="B197" s="2"/>
       <c r="C197" s="6"/>
@@ -5915,7 +5917,7 @@
       <c r="X197" s="1"/>
       <c r="Y197" s="1"/>
     </row>
-    <row r="198" spans="1:25" ht="15.75" customHeight="1">
+    <row r="198" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="1"/>
       <c r="B198" s="2"/>
       <c r="C198" s="6"/>
@@ -5942,7 +5944,7 @@
       <c r="X198" s="1"/>
       <c r="Y198" s="1"/>
     </row>
-    <row r="199" spans="1:25" ht="15.75" customHeight="1">
+    <row r="199" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="1"/>
       <c r="B199" s="2"/>
       <c r="C199" s="6"/>
@@ -5969,7 +5971,7 @@
       <c r="X199" s="1"/>
       <c r="Y199" s="1"/>
     </row>
-    <row r="200" spans="1:25" ht="15.75" customHeight="1">
+    <row r="200" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="1"/>
       <c r="B200" s="2"/>
       <c r="C200" s="6"/>
@@ -5996,7 +5998,7 @@
       <c r="X200" s="1"/>
       <c r="Y200" s="1"/>
     </row>
-    <row r="201" spans="1:25" ht="15.75" customHeight="1">
+    <row r="201" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="1"/>
       <c r="B201" s="2"/>
       <c r="C201" s="6"/>
@@ -6023,7 +6025,7 @@
       <c r="X201" s="1"/>
       <c r="Y201" s="1"/>
     </row>
-    <row r="202" spans="1:25" ht="15.75" customHeight="1">
+    <row r="202" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="1"/>
       <c r="B202" s="2"/>
       <c r="C202" s="6"/>
@@ -6050,7 +6052,7 @@
       <c r="X202" s="1"/>
       <c r="Y202" s="1"/>
     </row>
-    <row r="203" spans="1:25" ht="15.75" customHeight="1">
+    <row r="203" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="1"/>
       <c r="B203" s="2"/>
       <c r="C203" s="6"/>
@@ -6077,7 +6079,7 @@
       <c r="X203" s="1"/>
       <c r="Y203" s="1"/>
     </row>
-    <row r="204" spans="1:25" ht="15.75" customHeight="1">
+    <row r="204" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="1"/>
       <c r="B204" s="2"/>
       <c r="C204" s="6"/>
@@ -6104,7 +6106,7 @@
       <c r="X204" s="1"/>
       <c r="Y204" s="1"/>
     </row>
-    <row r="205" spans="1:25" ht="15.75" customHeight="1">
+    <row r="205" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="1"/>
       <c r="B205" s="2"/>
       <c r="C205" s="6"/>
@@ -6131,7 +6133,7 @@
       <c r="X205" s="1"/>
       <c r="Y205" s="1"/>
     </row>
-    <row r="206" spans="1:25" ht="15.75" customHeight="1">
+    <row r="206" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="1"/>
       <c r="B206" s="2"/>
       <c r="C206" s="6"/>
@@ -6158,7 +6160,7 @@
       <c r="X206" s="1"/>
       <c r="Y206" s="1"/>
     </row>
-    <row r="207" spans="1:25" ht="15.75" customHeight="1">
+    <row r="207" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="1"/>
       <c r="B207" s="2"/>
       <c r="C207" s="6"/>
@@ -6185,7 +6187,7 @@
       <c r="X207" s="1"/>
       <c r="Y207" s="1"/>
     </row>
-    <row r="208" spans="1:25" ht="15.75" customHeight="1">
+    <row r="208" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="1"/>
       <c r="B208" s="2"/>
       <c r="C208" s="6"/>
@@ -6212,7 +6214,7 @@
       <c r="X208" s="1"/>
       <c r="Y208" s="1"/>
     </row>
-    <row r="209" spans="1:25" ht="15.75" customHeight="1">
+    <row r="209" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="1"/>
       <c r="B209" s="2"/>
       <c r="C209" s="6"/>
@@ -6239,7 +6241,7 @@
       <c r="X209" s="1"/>
       <c r="Y209" s="1"/>
     </row>
-    <row r="210" spans="1:25" ht="15.75" customHeight="1">
+    <row r="210" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="1"/>
       <c r="B210" s="2"/>
       <c r="C210" s="6"/>
@@ -6266,7 +6268,7 @@
       <c r="X210" s="1"/>
       <c r="Y210" s="1"/>
     </row>
-    <row r="211" spans="1:25" ht="15.75" customHeight="1">
+    <row r="211" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="1"/>
       <c r="B211" s="2"/>
       <c r="C211" s="6"/>
@@ -6293,7 +6295,7 @@
       <c r="X211" s="1"/>
       <c r="Y211" s="1"/>
     </row>
-    <row r="212" spans="1:25" ht="15.75" customHeight="1">
+    <row r="212" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="1"/>
       <c r="B212" s="2"/>
       <c r="C212" s="6"/>
@@ -6320,7 +6322,7 @@
       <c r="X212" s="1"/>
       <c r="Y212" s="1"/>
     </row>
-    <row r="213" spans="1:25" ht="15.75" customHeight="1">
+    <row r="213" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="1"/>
       <c r="B213" s="2"/>
       <c r="C213" s="6"/>
@@ -6347,7 +6349,7 @@
       <c r="X213" s="1"/>
       <c r="Y213" s="1"/>
     </row>
-    <row r="214" spans="1:25" ht="15.75" customHeight="1">
+    <row r="214" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="1"/>
       <c r="B214" s="2"/>
       <c r="C214" s="6"/>
@@ -6374,7 +6376,7 @@
       <c r="X214" s="1"/>
       <c r="Y214" s="1"/>
     </row>
-    <row r="215" spans="1:25" ht="15.75" customHeight="1">
+    <row r="215" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="1"/>
       <c r="B215" s="2"/>
       <c r="C215" s="6"/>
@@ -6401,7 +6403,7 @@
       <c r="X215" s="1"/>
       <c r="Y215" s="1"/>
     </row>
-    <row r="216" spans="1:25" ht="15.75" customHeight="1">
+    <row r="216" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="1"/>
       <c r="B216" s="2"/>
       <c r="C216" s="6"/>
@@ -6428,7 +6430,7 @@
       <c r="X216" s="1"/>
       <c r="Y216" s="1"/>
     </row>
-    <row r="217" spans="1:25" ht="15.75" customHeight="1">
+    <row r="217" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="1"/>
       <c r="B217" s="2"/>
       <c r="C217" s="6"/>
@@ -6455,7 +6457,7 @@
       <c r="X217" s="1"/>
       <c r="Y217" s="1"/>
     </row>
-    <row r="218" spans="1:25" ht="15.75" customHeight="1">
+    <row r="218" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="1"/>
       <c r="B218" s="2"/>
       <c r="C218" s="6"/>
@@ -6482,7 +6484,7 @@
       <c r="X218" s="1"/>
       <c r="Y218" s="1"/>
     </row>
-    <row r="219" spans="1:25" ht="15.75" customHeight="1">
+    <row r="219" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="1"/>
       <c r="B219" s="2"/>
       <c r="C219" s="6"/>
@@ -6509,7 +6511,7 @@
       <c r="X219" s="1"/>
       <c r="Y219" s="1"/>
     </row>
-    <row r="220" spans="1:25" ht="15.75" customHeight="1">
+    <row r="220" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="1"/>
       <c r="B220" s="2"/>
       <c r="C220" s="6"/>
@@ -6536,786 +6538,786 @@
       <c r="X220" s="1"/>
       <c r="Y220" s="1"/>
     </row>
-    <row r="221" spans="1:25" ht="15.75" customHeight="1"/>
-    <row r="222" spans="1:25" ht="15.75" customHeight="1"/>
-    <row r="223" spans="1:25" ht="15.75" customHeight="1"/>
-    <row r="224" spans="1:25" ht="15.75" customHeight="1"/>
-    <row r="225" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="226" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="227" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="228" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="229" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="230" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="231" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="232" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="233" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="234" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="235" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="236" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="237" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="238" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="239" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="240" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="241" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="242" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="243" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="244" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="245" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="246" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="247" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="248" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="249" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="250" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="251" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="252" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="253" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="254" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="255" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="256" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="257" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="258" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="259" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="260" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="261" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="262" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="263" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="264" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="265" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="266" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="267" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="268" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="269" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="270" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="271" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="272" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="273" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="274" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="275" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="276" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="277" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="278" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="279" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="280" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="281" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="282" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="283" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="284" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="285" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="286" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="287" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="288" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="289" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="290" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="291" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="292" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="293" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="294" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="295" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="296" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="297" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="298" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="299" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="300" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="301" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="302" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="303" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="304" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="305" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="306" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="307" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="308" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="309" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="310" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="311" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="312" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="313" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="314" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="315" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="316" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="317" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="318" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="319" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="320" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="321" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="322" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="323" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="324" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="325" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="326" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="327" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="328" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="329" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="330" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="331" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="332" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="333" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="334" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="335" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="336" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="337" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="338" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="339" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="340" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="341" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="342" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="343" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="344" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="345" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="346" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="347" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="348" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="349" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="350" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="351" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="352" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="353" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="354" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="355" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="356" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="357" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="358" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="359" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="360" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="361" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="362" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="363" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="364" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="365" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="366" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="367" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="368" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="369" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="370" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="371" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="372" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="373" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="374" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="375" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="376" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="377" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="378" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="379" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="380" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="381" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="382" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="383" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="384" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="385" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="386" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="387" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="388" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="389" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="390" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="391" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="392" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="393" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="394" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="395" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="396" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="397" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="398" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="399" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="400" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="401" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="402" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="403" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="404" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="405" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="406" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="407" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="408" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="409" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="410" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="411" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="412" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="413" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="414" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="415" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="416" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="417" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="418" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="419" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="420" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="421" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="422" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="423" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="424" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="425" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="426" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="427" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="428" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="429" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="430" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="431" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="432" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="433" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="434" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="435" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="436" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="437" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="438" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="439" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="440" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="441" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="442" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="443" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="444" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="445" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="446" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="447" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="448" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="449" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="450" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="451" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="452" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="453" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="454" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="455" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="456" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="457" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="458" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="459" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="460" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="461" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="462" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="463" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="464" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="465" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="466" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="467" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="468" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="469" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="470" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="471" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="472" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="473" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="474" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="475" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="476" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="477" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="478" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="479" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="480" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="481" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="482" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="483" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="484" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="485" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="486" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="487" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="488" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="489" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="490" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="491" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="492" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="493" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="494" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="495" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="496" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="497" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="498" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="499" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="500" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="501" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="502" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="503" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="504" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="505" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="506" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="507" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="508" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="509" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="510" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="511" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="512" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="513" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="514" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="515" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="516" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="517" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="518" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="519" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="520" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="521" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="522" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="523" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="524" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="525" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="526" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="527" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="528" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="529" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="530" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="531" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="532" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="533" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="534" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="535" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="536" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="537" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="538" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="539" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="540" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="541" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="542" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="543" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="544" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="545" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="546" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="547" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="548" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="549" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="550" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="551" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="552" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="553" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="554" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="555" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="556" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="557" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="558" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="559" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="560" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="561" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="562" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="563" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="564" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="565" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="566" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="567" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="568" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="569" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="570" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="571" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="572" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="573" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="574" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="575" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="576" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="577" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="578" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="579" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="580" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="581" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="582" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="583" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="584" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="585" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="586" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="587" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="588" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="589" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="590" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="591" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="592" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="593" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="594" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="595" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="596" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="597" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="598" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="599" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="600" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="601" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="602" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="603" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="604" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="605" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="606" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="607" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="608" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="609" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="610" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="611" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="612" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="613" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="614" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="615" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="616" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="617" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="618" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="619" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="620" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="621" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="622" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="623" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="624" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="625" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="626" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="627" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="628" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="629" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="630" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="631" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="632" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="633" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="634" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="635" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="636" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="637" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="638" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="639" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="640" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="641" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="642" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="643" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="644" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="645" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="646" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="647" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="648" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="649" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="650" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="651" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="652" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="653" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="654" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="655" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="656" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="657" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="658" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="659" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="660" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="661" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="662" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="663" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="664" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="665" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="666" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="667" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="668" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="669" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="670" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="671" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="672" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="673" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="674" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="675" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="676" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="677" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="678" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="679" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="680" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="681" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="682" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="683" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="684" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="685" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="686" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="687" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="688" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="689" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="690" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="691" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="692" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="693" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="694" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="695" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="696" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="697" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="698" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="699" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="700" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="701" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="702" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="703" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="704" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="705" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="706" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="707" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="708" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="709" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="710" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="711" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="712" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="713" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="714" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="715" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="716" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="717" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="718" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="719" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="720" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="721" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="722" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="723" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="724" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="725" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="726" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="727" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="728" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="729" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="730" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="731" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="732" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="733" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="734" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="735" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="736" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="737" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="738" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="739" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="740" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="741" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="742" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="743" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="744" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="745" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="746" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="747" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="748" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="749" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="750" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="751" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="752" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="753" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="754" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="755" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="756" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="757" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="758" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="759" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="760" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="761" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="762" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="763" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="764" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="765" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="766" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="767" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="768" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="769" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="770" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="771" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="772" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="773" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="774" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="775" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="776" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="777" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="778" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="779" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="780" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="781" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="782" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="783" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="784" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="785" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="786" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="787" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="788" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="789" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="790" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="791" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="792" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="793" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="794" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="795" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="796" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="797" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="798" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="799" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="800" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="801" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="802" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="803" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="804" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="805" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="806" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="807" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="808" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="809" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="810" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="811" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="812" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="813" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="814" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="815" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="816" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="817" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="818" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="819" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="820" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="821" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="822" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="823" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="824" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="825" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="826" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="827" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="828" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="829" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="830" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="831" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="832" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="833" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="834" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="835" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="836" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="837" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="838" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="839" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="840" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="841" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="842" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="843" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="844" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="845" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="846" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="847" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="848" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="849" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="850" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="851" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="852" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="853" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="854" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="855" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="856" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="857" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="858" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="859" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="860" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="861" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="862" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="863" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="864" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="865" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="866" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="867" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="868" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="869" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="870" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="871" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="872" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="873" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="874" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="875" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="876" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="877" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="878" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="879" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="880" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="881" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="882" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="883" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="884" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="885" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="886" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="887" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="888" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="889" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="890" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="891" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="892" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="893" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="894" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="895" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="896" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="897" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="898" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="899" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="900" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="901" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="902" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="903" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="904" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="905" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="906" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="907" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="908" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="909" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="910" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="911" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="912" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="913" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="914" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="915" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="916" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="917" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="918" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="919" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="920" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="921" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="922" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="923" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="924" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="925" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="926" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="927" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="928" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="929" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="930" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="931" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="932" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="933" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="934" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="935" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="936" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="937" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="938" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="939" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="940" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="941" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="942" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="943" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="944" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="945" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="946" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="947" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="948" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="949" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="950" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="951" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="952" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="953" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="954" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="955" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="956" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="957" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="958" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="959" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="960" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="961" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="962" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="963" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="964" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="965" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="966" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="967" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="968" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="969" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="970" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="971" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="972" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="973" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="974" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="975" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="976" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="977" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="978" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="979" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="980" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="981" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="982" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="983" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="984" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="985" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="986" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="987" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="988" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="989" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="990" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="991" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="992" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="993" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="994" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="995" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="996" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="997" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="998" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="999" customFormat="1" ht="15.75" customHeight="1"/>
-    <row r="1000" customFormat="1" ht="15.75" customHeight="1"/>
+    <row r="221" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
